--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487752_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487752_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7327</v>
+        <v>2.5687</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0626</v>
+        <v>1.7623</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6701</v>
+        <v>0.8064</v>
       </c>
       <c r="G2" t="n">
         <v>2.7208</v>
@@ -610,13 +610,13 @@
         <v>0.194</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1761</v>
+        <v>0.0121</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4856</v>
+        <v>0.1853</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3095</v>
+        <v>-0.1733</v>
       </c>
       <c r="V2" t="n">
         <v>0.6119</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1926</v>
+        <v>1.156</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9215</v>
+        <v>1.7213</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7289</v>
+        <v>-0.5654</v>
       </c>
       <c r="G3" t="n">
         <v>1.5498</v>
@@ -688,13 +688,13 @@
         <v>1.9403</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2548</v>
+        <v>0.2181</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6079</v>
+        <v>0.4077</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.353</v>
+        <v>-0.1895</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6119</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. GUEYE</t>
+          <t>D. LORENZO  NEGRETE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6082</v>
+        <v>0.2644</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4217</v>
+        <v>4.9376</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.8135</v>
+        <v>-4.6732</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9038</v>
+        <v>0.4933</v>
       </c>
       <c r="H4" t="n">
-        <v>2.5845</v>
+        <v>0.7769</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.6806</v>
+        <v>-0.2836</v>
       </c>
       <c r="J4" t="n">
-        <v>4.8614</v>
+        <v>3.911</v>
       </c>
       <c r="K4" t="n">
-        <v>4.6178</v>
+        <v>1.9979</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2436</v>
+        <v>1.9131</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.9576</v>
+        <v>-3.4177</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.0333</v>
+        <v>-1.221</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.9242</v>
+        <v>-2.1967</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.1344</v>
+        <v>0.9702</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.8806</v>
+        <v>-0.9702</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7463</v>
+        <v>1.9403</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3701</v>
+        <v>0.0726</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9724</v>
+        <v>0.5386</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3978</v>
+        <v>-0.466</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4686</v>
+        <v>-1.2716</v>
       </c>
       <c r="W4" t="n">
-        <v>0.4686</v>
+        <v>1.4582</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-2.7298</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. GARCIA BENITO</t>
+          <t>B. GUEYE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4609</v>
+        <v>-0.0191</v>
       </c>
       <c r="E5" t="n">
-        <v>3.089</v>
+        <v>2.1214</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.5498</v>
+        <v>-2.1406</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3137</v>
+        <v>0.9038</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0091</v>
+        <v>2.5845</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3047</v>
+        <v>-1.6806</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8703</v>
+        <v>4.8614</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0206</v>
+        <v>4.6178</v>
       </c>
       <c r="L5" t="n">
-        <v>1.8497</v>
+        <v>0.2436</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5565</v>
+        <v>-3.9576</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0115</v>
+        <v>-2.0333</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.545</v>
+        <v>-1.9242</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5821</v>
+        <v>-2.1344</v>
       </c>
       <c r="Q5" t="n">
+        <v>-3.8806</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.7463</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.7428</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.6721</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.0707</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.4686</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.4686</v>
+      </c>
+      <c r="X5" t="n">
         <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.5821</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.0911</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.6068</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-0.5157</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-2.4477</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.6119</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-3.0597</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.586</v>
+        <v>-0.5132</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3022</v>
+        <v>-0.2021</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2838</v>
+        <v>-0.3111</v>
       </c>
       <c r="G6" t="n">
         <v>-0.7013</v>
@@ -922,13 +922,13 @@
         <v>0.194</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.0059</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3634</v>
+        <v>-0.2633</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2847</v>
+        <v>0.2574</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. LORENZO  NEGRETE</t>
+          <t>I. GARCIA BENITO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7727000000000001</v>
+        <v>-0.5337</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0367</v>
+        <v>2.9889</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.8095</v>
+        <v>-3.5226</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4933</v>
+        <v>1.3137</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7769</v>
+        <v>0.0091</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2836</v>
+        <v>1.3047</v>
       </c>
       <c r="J7" t="n">
-        <v>3.911</v>
+        <v>1.8703</v>
       </c>
       <c r="K7" t="n">
-        <v>1.9979</v>
+        <v>0.0206</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9131</v>
+        <v>1.8497</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.4177</v>
+        <v>-0.5565</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.221</v>
+        <v>-0.0115</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.1967</v>
+        <v>-0.545</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9702</v>
+        <v>0.5821</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9403</v>
+        <v>0.5821</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9645</v>
+        <v>0.0182</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3623</v>
+        <v>0.5067</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6022</v>
+        <v>-0.4884</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2716</v>
+        <v>-2.4477</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4582</v>
+        <v>0.6119</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.7298</v>
+        <v>-3.0597</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6908</v>
+        <v>-2.773</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8746</v>
+        <v>0.1739</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.5654</v>
+        <v>-2.947</v>
       </c>
       <c r="G8" t="n">
         <v>-5.4141</v>
@@ -1078,13 +1078,13 @@
         <v>2.1344</v>
       </c>
       <c r="S8" t="n">
-        <v>1.7218</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>1.7608</v>
+        <v>1.0601</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.039</v>
+        <v>-0.4206</v>
       </c>
       <c r="V8" t="n">
         <v>2.7776</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. KLOTZ MAROTO</t>
+          <t>C. UNANUE CEGARRA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.4033</v>
+        <v>-3.5719</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1696</v>
+        <v>-4.3181</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.2337</v>
+        <v>0.7461</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.7857</v>
+        <v>-4.7106</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.524</v>
+        <v>-1.3973</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.2617</v>
+        <v>-3.3133</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2611</v>
+        <v>-4.0737</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6344</v>
+        <v>-0.1153</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6267</v>
+        <v>-3.9583</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5246</v>
+        <v>-0.6369</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1104</v>
+        <v>-1.282</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.635</v>
+        <v>0.645</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5821</v>
+        <v>0.194</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3881</v>
+        <v>1.1642</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1884</v>
+        <v>-0.2793</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0617</v>
+        <v>-0.1683</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1267</v>
+        <v>-0.111</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2239</v>
+        <v>1.2239</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.894</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2239</v>
+        <v>0.3299</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. UNANUE CEGARRA</t>
+          <t>C. KLOTZ MAROTO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.4817</v>
+        <v>-4.4672</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.1189</v>
+        <v>-2.3698</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6371</v>
+        <v>-2.0974</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.7106</v>
+        <v>-2.7857</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.3973</v>
+        <v>-0.524</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.3133</v>
+        <v>-2.2617</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.0737</v>
+        <v>-1.2611</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1153</v>
+        <v>-0.6344</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.9583</v>
+        <v>-0.6267</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6369</v>
+        <v>-1.5246</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.282</v>
+        <v>0.1104</v>
       </c>
       <c r="O10" t="n">
-        <v>0.645</v>
+        <v>-1.635</v>
       </c>
       <c r="P10" t="n">
-        <v>0.194</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1642</v>
+        <v>0.3881</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1891</v>
+        <v>0.1245</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9691</v>
+        <v>-0.1385</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.22</v>
+        <v>0.263</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2239</v>
+        <v>-1.2239</v>
       </c>
       <c r="W10" t="n">
-        <v>0.894</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3299</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.1296</v>
+        <v>-6.1024</v>
       </c>
       <c r="E11" t="n">
         <v>-1.8856</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.244</v>
+        <v>-4.2168</v>
       </c>
       <c r="G11" t="n">
         <v>-1.0968</v>
@@ -1312,13 +1312,13 @@
         <v>1.3582</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.297</v>
+        <v>-0.2697</v>
       </c>
       <c r="T11" t="n">
         <v>-0.12</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.177</v>
+        <v>-0.1497</v>
       </c>
       <c r="V11" t="n">
         <v>-2.2134</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-13.9915</v>
+        <v>-13.9914</v>
       </c>
       <c r="E12" t="n">
         <v>4.9298</v>
       </c>
       <c r="F12" t="n">
-        <v>-18.9214</v>
+        <v>-18.9216</v>
       </c>
       <c r="G12" t="n">
         <v>-7.7271</v>
@@ -1396,10 +1396,10 @@
         <v>2.6804</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.4072</v>
+        <v>-1.4074</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.686500000000001</v>
+        <v>-2.6865</v>
       </c>
       <c r="W12" t="n">
         <v>7.9028</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.8018</v>
+        <v>11.5932</v>
       </c>
       <c r="E13" t="n">
-        <v>9.9597</v>
+        <v>10.5603</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8421</v>
+        <v>1.0329</v>
       </c>
       <c r="G13" t="n">
         <v>5.7043</v>
@@ -1468,13 +1468,13 @@
         <v>2.1344</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9159</v>
+        <v>-0.1245</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8479</v>
+        <v>-0.2473</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0679</v>
+        <v>0.1228</v>
       </c>
       <c r="V13" t="n">
         <v>3.8791</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.1197</v>
+        <v>3.8645</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0073</v>
+        <v>3.5068</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1124</v>
+        <v>0.3576</v>
       </c>
       <c r="G14" t="n">
         <v>3.2639</v>
@@ -1546,13 +1546,13 @@
         <v>2.1344</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2005</v>
+        <v>-0.0547</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3656</v>
+        <v>-0.1349</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1651</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>1.4313</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9311</v>
+        <v>3.8404</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2955</v>
+        <v>2.796</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6356000000000001</v>
+        <v>1.0444</v>
       </c>
       <c r="G15" t="n">
         <v>2.0213</v>
@@ -1624,13 +1624,13 @@
         <v>2.1344</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1216</v>
+        <v>-0.2123</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0595</v>
+        <v>0.441</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0621</v>
+        <v>-0.6533</v>
       </c>
       <c r="V15" t="n">
         <v>0.8672</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4869</v>
+        <v>1.6133</v>
       </c>
       <c r="E16" t="n">
-        <v>4.735</v>
+        <v>3.8341</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.2481</v>
+        <v>-2.2208</v>
       </c>
       <c r="G16" t="n">
         <v>1.0222</v>
@@ -1702,13 +1702,13 @@
         <v>1.7463</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7348</v>
+        <v>-0.1388</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5791</v>
+        <v>0.6782</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8443000000000001</v>
+        <v>-0.8169999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>-1.0164</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8799</v>
+        <v>0.0073</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0363</v>
+        <v>-0.3366</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9162</v>
+        <v>0.3439</v>
       </c>
       <c r="G17" t="n">
         <v>-1.0976</v>
@@ -1780,13 +1780,13 @@
         <v>3.1045</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2178</v>
+        <v>0.3452</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9118000000000001</v>
+        <v>0.6115</v>
       </c>
       <c r="U17" t="n">
-        <v>0.306</v>
+        <v>-0.2663</v>
       </c>
       <c r="V17" t="n">
         <v>-0.4045</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. MANERO GUZMAN</t>
+          <t>E. DUQUE NEGRÍN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8747</v>
+        <v>-1.1374</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8625</v>
+        <v>1.3307</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7372</v>
+        <v>-2.4681</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.0257</v>
+        <v>-1.5472</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6854</v>
+        <v>-1.6807</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3402</v>
+        <v>0.1335</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5557</v>
+        <v>0.108</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6344</v>
+        <v>-0.1812</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.1901</v>
+        <v>0.2892</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.47</v>
+        <v>-1.6552</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3198</v>
+        <v>-1.4995</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1502</v>
+        <v>-0.1557</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.7463</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9702</v>
+        <v>2.7164</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4912</v>
+        <v>-0.4425</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0595</v>
+        <v>0.6869</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5507</v>
+        <v>-1.1294</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6597</v>
+        <v>-0.894</v>
       </c>
       <c r="W18" t="n">
-        <v>2.4477</v>
+        <v>1.506</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.788</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. DUQUE NEGRÍN</t>
+          <t>S. MANERO GUZMAN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3376</v>
+        <v>-1.3113</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1305</v>
+        <v>0.5622</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.4681</v>
+        <v>-1.8735</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.5472</v>
+        <v>-2.0257</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.6807</v>
+        <v>-0.6854</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1335</v>
+        <v>-1.3402</v>
       </c>
       <c r="J19" t="n">
-        <v>0.108</v>
+        <v>-0.5557</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1812</v>
+        <v>0.6344</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2892</v>
+        <v>-1.1901</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6552</v>
+        <v>-1.47</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.4995</v>
+        <v>-1.3198</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1557</v>
+        <v>-0.1502</v>
       </c>
       <c r="P19" t="n">
-        <v>1.7463</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R19" t="n">
-        <v>2.7164</v>
+        <v>0.9702</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6427</v>
+        <v>0.0547</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4867</v>
+        <v>-0.3598</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.1294</v>
+        <v>0.4144</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.894</v>
+        <v>0.6597</v>
       </c>
       <c r="W19" t="n">
-        <v>1.506</v>
+        <v>2.4477</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.4</v>
+        <v>-1.788</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.0157</v>
+        <v>-4.4785</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.703</v>
+        <v>-3.0023</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3127</v>
+        <v>-1.4762</v>
       </c>
       <c r="G20" t="n">
         <v>0.3858</v>
@@ -2014,13 +2014,13 @@
         <v>1.5523</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2373</v>
+        <v>-0.7000999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9691</v>
+        <v>-0.2684</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2683</v>
+        <v>-0.4318</v>
       </c>
       <c r="V20" t="n">
         <v>-1.8358</v>
@@ -2047,7 +2047,7 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>13.9914</v>
+        <v>13.9915</v>
       </c>
       <c r="E21" t="n">
         <v>19.2512</v>
@@ -2092,7 +2092,7 @@
         <v>16.4929</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2732</v>
+        <v>-1.273</v>
       </c>
       <c r="T21" t="n">
         <v>1.4072</v>
